--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_2/epoch_90/per_file_predictions_epoch_90.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_2/epoch_90/per_file_predictions_epoch_90.xlsx
@@ -865,7 +865,7 @@
     <t>0.7827,0.0159,0.1749,0.0028</t>
   </si>
   <si>
-    <t>0.0135,0.0530,0.9505,0.0019</t>
+    <t>0.0135,0.0530,0.9504,0.0019</t>
   </si>
   <si>
     <t>0.0947,0.0002,0.9535,0.0001</t>
@@ -922,7 +922,7 @@
     <t>0.0020,0.0002,0.9985,0.0002</t>
   </si>
   <si>
-    <t>0.0057,0.4875,0.8332,0.0022</t>
+    <t>0.0057,0.4876,0.8332,0.0022</t>
   </si>
   <si>
     <t>0.9385,0.0049,0.0281,0.0007</t>
@@ -958,7 +958,7 @@
     <t>0.0033,0.0096,0.9924,0.0014</t>
   </si>
   <si>
-    <t>0.0028,0.8748,0.0007,0.7905</t>
+    <t>0.0028,0.8748,0.0007,0.7906</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0003,0.0002</t>
@@ -1336,7 +1336,7 @@
     <t>0.9927,0.0018,0.0011,0.0003</t>
   </si>
   <si>
-    <t>0.7195,0.2660,0.0091,0.0114</t>
+    <t>0.7194,0.2660,0.0091,0.0114</t>
   </si>
   <si>
     <t>0.4244,0.6094,0.0076,0.0084</t>
@@ -1393,7 +1393,7 @@
     <t>0.1092,0.0026,0.9042,0.0019</t>
   </si>
   <si>
-    <t>0.6482,0.0653,0.2319,0.0082</t>
+    <t>0.6481,0.0654,0.2319,0.0082</t>
   </si>
   <si>
     <t>0.0282,0.0090,0.9673,0.0036</t>
@@ -1540,7 +1540,7 @@
     <t>0.9875,0.0032,0.0027,0.0009</t>
   </si>
   <si>
-    <t>0.0032,0.2063,0.8886,0.0021</t>
+    <t>0.0032,0.2064,0.8886,0.0021</t>
   </si>
   <si>
     <t>0.0018,0.0080,0.9980,0.0001</t>
@@ -1579,7 +1579,7 @@
     <t>0.0001,0.0012,0.0006,1.0000</t>
   </si>
   <si>
-    <t>0.6745,0.0066,0.0122,0.2666</t>
+    <t>0.6744,0.0066,0.0122,0.2666</t>
   </si>
 </sst>
 </file>

--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_2/epoch_90/per_file_predictions_epoch_90.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_2/epoch_90/per_file_predictions_epoch_90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="524">
   <si>
     <t>Filename</t>
   </si>
@@ -826,16 +826,22 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9379,0.0020,0.0144,0.0035</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9379,0.0020,0.0143,0.0035</t>
   </si>
   <si>
     <t>0.0017,0.0063,0.0003,0.9995</t>
   </si>
   <si>
-    <t>0.9466,0.0021,0.0011,0.0195</t>
-  </si>
-  <si>
-    <t>0.2091,0.0003,0.0007,0.8910</t>
+    <t>0.9465,0.0021,0.0011,0.0196</t>
+  </si>
+  <si>
+    <t>0.2087,0.0003,0.0007,0.8912</t>
   </si>
   <si>
     <t>0.9945,0.0018,0.0008,0.0002</t>
@@ -862,19 +868,19 @@
     <t>0.9913,0.0026,0.0018,0.0002</t>
   </si>
   <si>
-    <t>0.7827,0.0159,0.1749,0.0028</t>
-  </si>
-  <si>
-    <t>0.0135,0.0530,0.9504,0.0019</t>
+    <t>0.7830,0.0159,0.1746,0.0028</t>
+  </si>
+  <si>
+    <t>0.0135,0.0530,0.9503,0.0019</t>
   </si>
   <si>
     <t>0.0947,0.0002,0.9535,0.0001</t>
   </si>
   <si>
-    <t>0.0460,0.0031,0.9669,0.0010</t>
-  </si>
-  <si>
-    <t>0.8210,0.0006,0.2126,0.0002</t>
+    <t>0.0460,0.0031,0.9668,0.0010</t>
+  </si>
+  <si>
+    <t>0.8209,0.0006,0.2126,0.0002</t>
   </si>
   <si>
     <t>0.0004,0.9992,0.0005,0.0003</t>
@@ -883,7 +889,7 @@
     <t>0.0024,0.9963,0.0005,0.0012</t>
   </si>
   <si>
-    <t>0.0455,0.9771,0.0192,0.0002</t>
+    <t>0.0457,0.9770,0.0192,0.0002</t>
   </si>
   <si>
     <t>0.0040,0.9932,0.0009,0.0036</t>
@@ -892,7 +898,7 @@
     <t>0.0002,0.9997,0.0006,0.0000</t>
   </si>
   <si>
-    <t>0.2352,0.0023,0.8265,0.0013</t>
+    <t>0.2355,0.0023,0.8263,0.0013</t>
   </si>
   <si>
     <t>0.0834,0.0058,0.9315,0.0024</t>
@@ -913,16 +919,16 @@
     <t>0.0079,0.0003,0.9922,0.0011</t>
   </si>
   <si>
-    <t>0.6904,0.2508,0.0562,0.0025</t>
-  </si>
-  <si>
-    <t>0.8249,0.1904,0.0142,0.0008</t>
-  </si>
-  <si>
-    <t>0.0020,0.0002,0.9985,0.0002</t>
-  </si>
-  <si>
-    <t>0.0057,0.4876,0.8332,0.0022</t>
+    <t>0.6903,0.2510,0.0562,0.0025</t>
+  </si>
+  <si>
+    <t>0.8248,0.1903,0.0142,0.0008</t>
+  </si>
+  <si>
+    <t>0.0020,0.0002,0.9984,0.0002</t>
+  </si>
+  <si>
+    <t>0.0057,0.4878,0.8328,0.0022</t>
   </si>
   <si>
     <t>0.9385,0.0049,0.0281,0.0007</t>
@@ -937,19 +943,19 @@
     <t>0.0069,0.9493,0.7451,0.0006</t>
   </si>
   <si>
-    <t>0.0021,0.8745,0.9223,0.0007</t>
+    <t>0.0021,0.8743,0.9223,0.0007</t>
   </si>
   <si>
     <t>0.0015,0.0005,0.9974,0.0006</t>
   </si>
   <si>
-    <t>0.0111,0.0200,0.9698,0.0032</t>
-  </si>
-  <si>
-    <t>0.1496,0.0002,0.8483,0.0058</t>
-  </si>
-  <si>
-    <t>0.0020,0.3063,0.9787,0.0007</t>
+    <t>0.0111,0.0199,0.9698,0.0032</t>
+  </si>
+  <si>
+    <t>0.1498,0.0002,0.8480,0.0057</t>
+  </si>
+  <si>
+    <t>0.0020,0.3060,0.9787,0.0007</t>
   </si>
   <si>
     <t>0.0007,0.9957,0.0060,0.0045</t>
@@ -958,34 +964,34 @@
     <t>0.0033,0.0096,0.9924,0.0014</t>
   </si>
   <si>
-    <t>0.0028,0.8748,0.0007,0.7906</t>
+    <t>0.0028,0.8749,0.0007,0.7904</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0003,0.0002</t>
   </si>
   <si>
-    <t>0.0001,0.9996,0.1022,0.0001</t>
+    <t>0.0001,0.9996,0.1023,0.0001</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0103,0.0001</t>
   </si>
   <si>
-    <t>0.0008,0.0609,0.9941,0.0005</t>
-  </si>
-  <si>
-    <t>0.0009,0.0499,0.9960,0.0003</t>
+    <t>0.0008,0.0608,0.9941,0.0005</t>
+  </si>
+  <si>
+    <t>0.0009,0.0498,0.9960,0.0003</t>
   </si>
   <si>
     <t>0.0139,0.0017,0.9854,0.0022</t>
   </si>
   <si>
-    <t>0.0239,0.0001,0.9909,0.0001</t>
+    <t>0.0240,0.0001,0.9909,0.0001</t>
   </si>
   <si>
     <t>0.0061,0.0005,0.9954,0.0003</t>
   </si>
   <si>
-    <t>0.0325,0.0082,0.9585,0.0022</t>
+    <t>0.0325,0.0082,0.9584,0.0022</t>
   </si>
   <si>
     <t>0.9577,0.0185,0.0172,0.0004</t>
@@ -994,13 +1000,13 @@
     <t>0.9618,0.0014,0.0236,0.0002</t>
   </si>
   <si>
-    <t>0.9806,0.0035,0.0056,0.0012</t>
-  </si>
-  <si>
-    <t>0.4796,0.0007,0.6183,0.0003</t>
-  </si>
-  <si>
-    <t>0.9818,0.0012,0.0091,0.0002</t>
+    <t>0.9806,0.0035,0.0057,0.0012</t>
+  </si>
+  <si>
+    <t>0.4788,0.0007,0.6191,0.0003</t>
+  </si>
+  <si>
+    <t>0.9818,0.0012,0.0092,0.0002</t>
   </si>
   <si>
     <t>0.9854,0.0032,0.0061,0.0004</t>
@@ -1009,10 +1015,10 @@
     <t>0.9931,0.0010,0.0024,0.0001</t>
   </si>
   <si>
-    <t>0.0001,0.9978,0.9243,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0289,0.9985,0.0001</t>
+    <t>0.0001,0.9978,0.9244,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0288,0.9985,0.0001</t>
   </si>
   <si>
     <t>0.0029,0.0036,0.9953,0.0009</t>
@@ -1030,10 +1036,10 @@
     <t>0.0000,0.9999,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9723,0.0011,0.0234,0.0001</t>
-  </si>
-  <si>
-    <t>0.1647,0.0436,0.7942,0.0092</t>
+    <t>0.9722,0.0011,0.0234,0.0001</t>
+  </si>
+  <si>
+    <t>0.1644,0.0436,0.7944,0.0092</t>
   </si>
   <si>
     <t>0.0089,0.0039,0.9914,0.0015</t>
@@ -1048,7 +1054,7 @@
     <t>0.0000,0.9999,0.0332,0.0001</t>
   </si>
   <si>
-    <t>0.0003,0.9905,0.8592,0.0003</t>
+    <t>0.0003,0.9905,0.8591,0.0003</t>
   </si>
   <si>
     <t>0.0102,0.0097,0.0013,0.9881</t>
@@ -1057,7 +1063,7 @@
     <t>0.0002,0.0004,0.0001,1.0000</t>
   </si>
   <si>
-    <t>0.0004,0.0005,0.0002,0.9999</t>
+    <t>0.0004,0.0004,0.0002,0.9999</t>
   </si>
   <si>
     <t>0.0016,0.0009,0.0009,0.9997</t>
@@ -1072,19 +1078,19 @@
     <t>0.0001,0.9960,0.9629,0.0000</t>
   </si>
   <si>
-    <t>0.0006,0.4560,0.9940,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.9410,0.6115,0.0016</t>
-  </si>
-  <si>
-    <t>0.0005,0.9379,0.9817,0.0002</t>
+    <t>0.0006,0.4553,0.9940,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.9409,0.6116,0.0016</t>
+  </si>
+  <si>
+    <t>0.0005,0.9378,0.9817,0.0002</t>
   </si>
   <si>
     <t>0.0001,0.9932,0.9815,0.0000</t>
   </si>
   <si>
-    <t>0.0003,0.9928,0.8599,0.0001</t>
+    <t>0.0003,0.9927,0.8600,0.0001</t>
   </si>
   <si>
     <t>0.9939,0.0041,0.0004,0.0002</t>
@@ -1093,10 +1099,10 @@
     <t>0.9678,0.0334,0.0042,0.0009</t>
   </si>
   <si>
-    <t>0.9305,0.0661,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9864,0.0139,0.0015,0.0009</t>
+    <t>0.9304,0.0661,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9864,0.0138,0.0015,0.0009</t>
   </si>
   <si>
     <t>0.9866,0.0078,0.0028,0.0003</t>
@@ -1105,7 +1111,7 @@
     <t>0.9924,0.0024,0.0006,0.0005</t>
   </si>
   <si>
-    <t>0.9857,0.0025,0.0055,0.0006</t>
+    <t>0.9857,0.0025,0.0056,0.0006</t>
   </si>
   <si>
     <t>0.9915,0.0016,0.0012,0.0006</t>
@@ -1114,7 +1120,7 @@
     <t>0.9931,0.0019,0.0011,0.0005</t>
   </si>
   <si>
-    <t>0.9810,0.0118,0.0017,0.0003</t>
+    <t>0.9809,0.0118,0.0017,0.0003</t>
   </si>
   <si>
     <t>0.9937,0.0034,0.0006,0.0003</t>
@@ -1123,7 +1129,7 @@
     <t>0.9966,0.0012,0.0004,0.0001</t>
   </si>
   <si>
-    <t>0.9783,0.0068,0.0031,0.0019</t>
+    <t>0.9784,0.0068,0.0031,0.0019</t>
   </si>
   <si>
     <t>0.9947,0.0022,0.0003,0.0001</t>
@@ -1138,7 +1144,7 @@
     <t>0.0009,0.0001,0.9991,0.0001</t>
   </si>
   <si>
-    <t>0.0797,0.0008,0.9554,0.0005</t>
+    <t>0.0799,0.0008,0.9553,0.0005</t>
   </si>
   <si>
     <t>0.9398,0.0003,0.1015,0.0000</t>
@@ -1153,16 +1159,16 @@
     <t>0.0001,0.9999,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.5454,0.5899,0.0011,0.0003</t>
-  </si>
-  <si>
-    <t>0.0872,0.9230,0.0145,0.0024</t>
+    <t>0.5456,0.5897,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.0874,0.9228,0.0145,0.0024</t>
   </si>
   <si>
     <t>0.0003,0.9996,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.7071,0.3680,0.0259,0.0026</t>
+    <t>0.7074,0.3678,0.0259,0.0026</t>
   </si>
   <si>
     <t>0.1241,0.0126,0.8821,0.0042</t>
@@ -1171,13 +1177,13 @@
     <t>0.0382,0.0022,0.9671,0.0015</t>
   </si>
   <si>
-    <t>0.4127,0.0127,0.5824,0.0048</t>
+    <t>0.4129,0.0127,0.5821,0.0048</t>
   </si>
   <si>
     <t>0.1178,0.0113,0.8921,0.0051</t>
   </si>
   <si>
-    <t>0.0012,0.4888,0.7668,0.0291</t>
+    <t>0.0012,0.4888,0.7667,0.0291</t>
   </si>
   <si>
     <t>0.0000,0.9998,0.0048,0.0001</t>
@@ -1189,16 +1195,16 @@
     <t>0.0001,0.9993,0.0002,0.0027</t>
   </si>
   <si>
-    <t>0.0000,0.9992,0.0481,0.0009</t>
-  </si>
-  <si>
-    <t>0.0029,0.9925,0.1508,0.0006</t>
-  </si>
-  <si>
-    <t>0.6611,0.3007,0.0513,0.0012</t>
-  </si>
-  <si>
-    <t>0.4139,0.5981,0.0516,0.0068</t>
+    <t>0.0000,0.9992,0.0482,0.0009</t>
+  </si>
+  <si>
+    <t>0.0029,0.9924,0.1508,0.0006</t>
+  </si>
+  <si>
+    <t>0.6609,0.3007,0.0514,0.0012</t>
+  </si>
+  <si>
+    <t>0.4141,0.5979,0.0516,0.0068</t>
   </si>
   <si>
     <t>0.9943,0.0004,0.0022,0.0001</t>
@@ -1210,43 +1216,43 @@
     <t>0.9873,0.0059,0.0016,0.0006</t>
   </si>
   <si>
-    <t>0.9841,0.0023,0.0061,0.0004</t>
+    <t>0.9841,0.0023,0.0060,0.0004</t>
   </si>
   <si>
     <t>0.9955,0.0019,0.0005,0.0001</t>
   </si>
   <si>
-    <t>0.9719,0.0009,0.0112,0.0004</t>
+    <t>0.9718,0.0009,0.0113,0.0004</t>
   </si>
   <si>
     <t>0.9892,0.0020,0.0026,0.0004</t>
   </si>
   <si>
-    <t>0.9937,0.0012,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.0021,0.9262,0.9312,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.4645,0.9977,0.0000</t>
+    <t>0.9936,0.0012,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.0021,0.9261,0.9312,0.0005</t>
+  </si>
+  <si>
+    <t>0.0002,0.4638,0.9977,0.0000</t>
   </si>
   <si>
     <t>0.0002,0.0023,0.9987,0.0013</t>
   </si>
   <si>
-    <t>0.0048,0.0180,0.9940,0.0002</t>
-  </si>
-  <si>
-    <t>0.9500,0.0026,0.0433,0.0003</t>
-  </si>
-  <si>
-    <t>0.4788,0.2408,0.0890,0.0094</t>
-  </si>
-  <si>
-    <t>0.0910,0.0001,0.9409,0.0007</t>
-  </si>
-  <si>
-    <t>0.7624,0.0124,0.2008,0.0025</t>
+    <t>0.0048,0.0179,0.9940,0.0002</t>
+  </si>
+  <si>
+    <t>0.9498,0.0026,0.0435,0.0003</t>
+  </si>
+  <si>
+    <t>0.4788,0.2406,0.0891,0.0094</t>
+  </si>
+  <si>
+    <t>0.0912,0.0001,0.9408,0.0007</t>
+  </si>
+  <si>
+    <t>0.7624,0.0124,0.2007,0.0025</t>
   </si>
   <si>
     <t>0.0097,0.0002,0.0013,0.9983</t>
@@ -1261,7 +1267,7 @@
     <t>0.0038,0.0002,0.0004,0.9995</t>
   </si>
   <si>
-    <t>0.0001,0.9950,0.9678,0.0000</t>
+    <t>0.0001,0.9950,0.9679,0.0000</t>
   </si>
   <si>
     <t>0.9804,0.0008,0.0080,0.0005</t>
@@ -1282,34 +1288,34 @@
     <t>0.4864,0.0000,0.5645,0.0000</t>
   </si>
   <si>
-    <t>0.7355,0.0000,0.2778,0.0001</t>
+    <t>0.7354,0.0000,0.2780,0.0001</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9606,0.0001,0.0168,0.0003</t>
+    <t>0.9605,0.0001,0.0169,0.0003</t>
   </si>
   <si>
     <t>0.9888,0.0017,0.0018,0.0002</t>
   </si>
   <si>
-    <t>0.8404,0.0793,0.0193,0.0007</t>
+    <t>0.8402,0.0793,0.0194,0.0007</t>
   </si>
   <si>
     <t>0.9870,0.0011,0.0054,0.0002</t>
   </si>
   <si>
-    <t>0.9000,0.0363,0.0397,0.0026</t>
-  </si>
-  <si>
-    <t>0.0643,0.8990,0.0157,0.0277</t>
+    <t>0.8999,0.0363,0.0398,0.0026</t>
+  </si>
+  <si>
+    <t>0.0644,0.8989,0.0156,0.0277</t>
   </si>
   <si>
     <t>0.9185,0.0352,0.0282,0.0009</t>
   </si>
   <si>
-    <t>0.9390,0.0112,0.0337,0.0010</t>
+    <t>0.9389,0.0112,0.0337,0.0010</t>
   </si>
   <si>
     <t>0.9904,0.0063,0.0010,0.0002</t>
@@ -1318,7 +1324,7 @@
     <t>0.9930,0.0026,0.0004,0.0004</t>
   </si>
   <si>
-    <t>0.9868,0.0042,0.0033,0.0003</t>
+    <t>0.9868,0.0042,0.0034,0.0003</t>
   </si>
   <si>
     <t>0.9873,0.0012,0.0038,0.0003</t>
@@ -1336,31 +1342,31 @@
     <t>0.9927,0.0018,0.0011,0.0003</t>
   </si>
   <si>
-    <t>0.7194,0.2660,0.0091,0.0114</t>
-  </si>
-  <si>
-    <t>0.4244,0.6094,0.0076,0.0084</t>
-  </si>
-  <si>
-    <t>0.8812,0.1139,0.0030,0.0021</t>
-  </si>
-  <si>
-    <t>0.7807,0.0061,0.2072,0.0006</t>
-  </si>
-  <si>
-    <t>0.9808,0.0064,0.0057,0.0006</t>
-  </si>
-  <si>
-    <t>0.9370,0.0160,0.0264,0.0008</t>
-  </si>
-  <si>
-    <t>0.9796,0.0045,0.0073,0.0004</t>
-  </si>
-  <si>
-    <t>0.9030,0.0700,0.0310,0.0054</t>
-  </si>
-  <si>
-    <t>0.0038,0.0025,0.9976,0.0001</t>
+    <t>0.7199,0.2656,0.0091,0.0114</t>
+  </si>
+  <si>
+    <t>0.4249,0.6089,0.0076,0.0084</t>
+  </si>
+  <si>
+    <t>0.8811,0.1139,0.0030,0.0021</t>
+  </si>
+  <si>
+    <t>0.7805,0.0061,0.2074,0.0006</t>
+  </si>
+  <si>
+    <t>0.9807,0.0064,0.0057,0.0006</t>
+  </si>
+  <si>
+    <t>0.9369,0.0160,0.0265,0.0008</t>
+  </si>
+  <si>
+    <t>0.9795,0.0045,0.0073,0.0004</t>
+  </si>
+  <si>
+    <t>0.9029,0.0700,0.0311,0.0054</t>
+  </si>
+  <si>
+    <t>0.0038,0.0024,0.9976,0.0001</t>
   </si>
   <si>
     <t>0.9552,0.0125,0.0208,0.0003</t>
@@ -1369,13 +1375,13 @@
     <t>0.0006,0.0001,0.9995,0.0000</t>
   </si>
   <si>
-    <t>0.0004,0.0715,0.9790,0.0075</t>
+    <t>0.0004,0.0713,0.9790,0.0076</t>
   </si>
   <si>
     <t>0.0083,0.0014,0.9928,0.0012</t>
   </si>
   <si>
-    <t>0.0034,0.5405,0.9012,0.0009</t>
+    <t>0.0034,0.5396,0.9013,0.0009</t>
   </si>
   <si>
     <t>0.0034,0.0009,0.9977,0.0002</t>
@@ -1387,58 +1393,58 @@
     <t>0.0116,0.0003,0.9929,0.0003</t>
   </si>
   <si>
-    <t>0.0710,0.0018,0.9473,0.0016</t>
-  </si>
-  <si>
-    <t>0.1092,0.0026,0.9042,0.0019</t>
-  </si>
-  <si>
-    <t>0.6481,0.0654,0.2319,0.0082</t>
-  </si>
-  <si>
-    <t>0.0282,0.0090,0.9673,0.0036</t>
-  </si>
-  <si>
-    <t>0.0123,0.0489,0.9661,0.0007</t>
+    <t>0.0711,0.0018,0.9472,0.0016</t>
+  </si>
+  <si>
+    <t>0.1093,0.0026,0.9041,0.0019</t>
+  </si>
+  <si>
+    <t>0.6484,0.0653,0.2317,0.0082</t>
+  </si>
+  <si>
+    <t>0.0283,0.0090,0.9672,0.0036</t>
+  </si>
+  <si>
+    <t>0.0123,0.0489,0.9660,0.0007</t>
   </si>
   <si>
     <t>0.0641,0.0028,0.9400,0.0026</t>
   </si>
   <si>
-    <t>0.1443,0.0045,0.8685,0.0042</t>
-  </si>
-  <si>
-    <t>0.4175,0.0093,0.5980,0.0021</t>
-  </si>
-  <si>
-    <t>0.1793,0.8943,0.0022,0.0001</t>
+    <t>0.1444,0.0045,0.8684,0.0042</t>
+  </si>
+  <si>
+    <t>0.4177,0.0093,0.5977,0.0021</t>
+  </si>
+  <si>
+    <t>0.1795,0.8942,0.0022,0.0001</t>
   </si>
   <si>
     <t>0.0021,0.9973,0.0008,0.0003</t>
   </si>
   <si>
-    <t>0.0697,0.9534,0.0014,0.0007</t>
+    <t>0.0696,0.9534,0.0014,0.0007</t>
   </si>
   <si>
     <t>0.9637,0.0292,0.0070,0.0006</t>
   </si>
   <si>
-    <t>0.4835,0.5850,0.0097,0.0028</t>
-  </si>
-  <si>
-    <t>0.2998,0.6824,0.0161,0.0015</t>
-  </si>
-  <si>
-    <t>0.9438,0.0028,0.0381,0.0004</t>
-  </si>
-  <si>
-    <t>0.5123,0.0218,0.4098,0.0124</t>
-  </si>
-  <si>
-    <t>0.1571,0.0005,0.8763,0.0026</t>
-  </si>
-  <si>
-    <t>0.6793,0.0067,0.2343,0.0038</t>
+    <t>0.4836,0.5849,0.0097,0.0028</t>
+  </si>
+  <si>
+    <t>0.3000,0.6821,0.0161,0.0015</t>
+  </si>
+  <si>
+    <t>0.9436,0.0028,0.0382,0.0004</t>
+  </si>
+  <si>
+    <t>0.5125,0.0218,0.4095,0.0124</t>
+  </si>
+  <si>
+    <t>0.1572,0.0005,0.8762,0.0026</t>
+  </si>
+  <si>
+    <t>0.6793,0.0067,0.2344,0.0038</t>
   </si>
   <si>
     <t>0.0054,0.0005,0.9948,0.0010</t>
@@ -1447,13 +1453,13 @@
     <t>0.0268,0.0028,0.9813,0.0012</t>
   </si>
   <si>
-    <t>0.0275,0.0118,0.9740,0.0006</t>
+    <t>0.0275,0.0117,0.9739,0.0006</t>
   </si>
   <si>
     <t>0.0063,0.0025,0.9929,0.0005</t>
   </si>
   <si>
-    <t>0.0529,0.0025,0.9552,0.0001</t>
+    <t>0.0530,0.0025,0.9551,0.0001</t>
   </si>
   <si>
     <t>0.9938,0.0007,0.0017,0.0002</t>
@@ -1471,7 +1477,7 @@
     <t>0.9319,0.0509,0.0153,0.0048</t>
   </si>
   <si>
-    <t>0.9608,0.0288,0.0063,0.0034</t>
+    <t>0.9607,0.0288,0.0063,0.0034</t>
   </si>
   <si>
     <t>0.9803,0.0090,0.0035,0.0007</t>
@@ -1480,10 +1486,10 @@
     <t>0.9949,0.0009,0.0012,0.0001</t>
   </si>
   <si>
-    <t>0.0114,0.0006,0.9930,0.0003</t>
-  </si>
-  <si>
-    <t>0.0714,0.0123,0.9335,0.0029</t>
+    <t>0.0115,0.0006,0.9930,0.0003</t>
+  </si>
+  <si>
+    <t>0.0715,0.0123,0.9333,0.0029</t>
   </si>
   <si>
     <t>0.4791,0.0083,0.4180,0.0175</t>
@@ -1495,22 +1501,22 @@
     <t>0.0003,0.0015,0.9993,0.0004</t>
   </si>
   <si>
-    <t>0.0068,0.0177,0.9813,0.0011</t>
+    <t>0.0068,0.0176,0.9812,0.0011</t>
   </si>
   <si>
     <t>0.0144,0.0072,0.9837,0.0013</t>
   </si>
   <si>
-    <t>0.0031,0.0021,0.9960,0.0005</t>
-  </si>
-  <si>
-    <t>0.0297,0.0165,0.9507,0.0074</t>
-  </si>
-  <si>
-    <t>0.7010,0.0010,0.3224,0.0018</t>
-  </si>
-  <si>
-    <t>0.3788,0.0007,0.5436,0.0132</t>
+    <t>0.0031,0.0020,0.9960,0.0005</t>
+  </si>
+  <si>
+    <t>0.0297,0.0165,0.9506,0.0074</t>
+  </si>
+  <si>
+    <t>0.7010,0.0010,0.3223,0.0018</t>
+  </si>
+  <si>
+    <t>0.3787,0.0007,0.5437,0.0132</t>
   </si>
   <si>
     <t>0.9306,0.0054,0.0476,0.0004</t>
@@ -1525,13 +1531,13 @@
     <t>0.9908,0.0074,0.0010,0.0002</t>
   </si>
   <si>
-    <t>0.9350,0.0583,0.0109,0.0019</t>
+    <t>0.9351,0.0582,0.0109,0.0019</t>
   </si>
   <si>
     <t>0.9940,0.0009,0.0016,0.0002</t>
   </si>
   <si>
-    <t>0.9820,0.0163,0.0022,0.0006</t>
+    <t>0.9821,0.0162,0.0022,0.0006</t>
   </si>
   <si>
     <t>0.9891,0.0076,0.0014,0.0009</t>
@@ -1540,7 +1546,7 @@
     <t>0.9875,0.0032,0.0027,0.0009</t>
   </si>
   <si>
-    <t>0.0032,0.2064,0.8886,0.0021</t>
+    <t>0.0032,0.2062,0.8885,0.0021</t>
   </si>
   <si>
     <t>0.0018,0.0080,0.9980,0.0001</t>
@@ -1555,16 +1561,16 @@
     <t>0.0088,0.0002,0.9953,0.0001</t>
   </si>
   <si>
-    <t>0.0741,0.0121,0.1329,0.5386</t>
-  </si>
-  <si>
-    <t>0.0801,0.0080,0.9190,0.0076</t>
+    <t>0.0740,0.0120,0.1332,0.5379</t>
+  </si>
+  <si>
+    <t>0.0803,0.0080,0.9189,0.0076</t>
   </si>
   <si>
     <t>0.0012,0.0000,0.9970,0.0018</t>
   </si>
   <si>
-    <t>0.9682,0.0004,0.0051,0.0027</t>
+    <t>0.9681,0.0004,0.0051,0.0027</t>
   </si>
   <si>
     <t>0.0004,0.0107,0.0001,0.9999</t>
@@ -1579,7 +1585,7 @@
     <t>0.0001,0.0012,0.0006,1.0000</t>
   </si>
   <si>
-    <t>0.6744,0.0066,0.0122,0.2666</t>
+    <t>0.6742,0.0066,0.0122,0.2666</t>
   </si>
 </sst>
 </file>
@@ -1965,7 +1971,7 @@
         <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1979,7 +1985,7 @@
         <v>265</v>
       </c>
       <c r="D3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1993,7 +1999,7 @@
         <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2007,7 +2013,7 @@
         <v>265</v>
       </c>
       <c r="D5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2021,7 +2027,7 @@
         <v>264</v>
       </c>
       <c r="D6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2035,7 +2041,7 @@
         <v>264</v>
       </c>
       <c r="D7" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2049,7 +2055,7 @@
         <v>264</v>
       </c>
       <c r="D8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2063,7 +2069,7 @@
         <v>264</v>
       </c>
       <c r="D9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2077,7 +2083,7 @@
         <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2091,7 +2097,7 @@
         <v>264</v>
       </c>
       <c r="D11" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2105,7 +2111,7 @@
         <v>264</v>
       </c>
       <c r="D12" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2119,7 +2125,7 @@
         <v>264</v>
       </c>
       <c r="D13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2133,7 +2139,7 @@
         <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2147,7 +2153,7 @@
         <v>266</v>
       </c>
       <c r="D15" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2161,7 +2167,7 @@
         <v>266</v>
       </c>
       <c r="D16" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2175,7 +2181,7 @@
         <v>266</v>
       </c>
       <c r="D17" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2189,7 +2195,7 @@
         <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2203,7 +2209,7 @@
         <v>267</v>
       </c>
       <c r="D19" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2217,7 +2223,7 @@
         <v>267</v>
       </c>
       <c r="D20" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2231,7 +2237,7 @@
         <v>267</v>
       </c>
       <c r="D21" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2245,7 +2251,7 @@
         <v>267</v>
       </c>
       <c r="D22" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2259,7 +2265,7 @@
         <v>267</v>
       </c>
       <c r="D23" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2273,7 +2279,7 @@
         <v>266</v>
       </c>
       <c r="D24" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2287,7 +2293,7 @@
         <v>266</v>
       </c>
       <c r="D25" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2301,7 +2307,7 @@
         <v>266</v>
       </c>
       <c r="D26" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2315,7 +2321,7 @@
         <v>266</v>
       </c>
       <c r="D27" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2329,7 +2335,7 @@
         <v>266</v>
       </c>
       <c r="D28" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2343,7 +2349,7 @@
         <v>266</v>
       </c>
       <c r="D29" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2357,7 +2363,7 @@
         <v>266</v>
       </c>
       <c r="D30" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2371,7 +2377,7 @@
         <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2385,7 +2391,7 @@
         <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2399,7 +2405,7 @@
         <v>266</v>
       </c>
       <c r="D33" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2413,7 +2419,7 @@
         <v>266</v>
       </c>
       <c r="D34" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2427,7 +2433,7 @@
         <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2441,7 +2447,7 @@
         <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2455,7 +2461,7 @@
         <v>267</v>
       </c>
       <c r="D37" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2469,7 +2475,7 @@
         <v>268</v>
       </c>
       <c r="D38" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2483,7 +2489,7 @@
         <v>268</v>
       </c>
       <c r="D39" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2497,7 +2503,7 @@
         <v>266</v>
       </c>
       <c r="D40" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2511,7 +2517,7 @@
         <v>266</v>
       </c>
       <c r="D41" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2525,7 +2531,7 @@
         <v>266</v>
       </c>
       <c r="D42" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2539,7 +2545,7 @@
         <v>266</v>
       </c>
       <c r="D43" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2553,7 +2559,7 @@
         <v>267</v>
       </c>
       <c r="D44" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2567,7 +2573,7 @@
         <v>266</v>
       </c>
       <c r="D45" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2581,7 +2587,7 @@
         <v>269</v>
       </c>
       <c r="D46" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2595,7 +2601,7 @@
         <v>267</v>
       </c>
       <c r="D47" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2609,7 +2615,7 @@
         <v>267</v>
       </c>
       <c r="D48" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2623,7 +2629,7 @@
         <v>267</v>
       </c>
       <c r="D49" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2637,7 +2643,7 @@
         <v>266</v>
       </c>
       <c r="D50" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2651,7 +2657,7 @@
         <v>266</v>
       </c>
       <c r="D51" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2665,7 +2671,7 @@
         <v>266</v>
       </c>
       <c r="D52" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2679,7 +2685,7 @@
         <v>266</v>
       </c>
       <c r="D53" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2693,7 +2699,7 @@
         <v>266</v>
       </c>
       <c r="D54" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2707,7 +2713,7 @@
         <v>266</v>
       </c>
       <c r="D55" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2721,7 +2727,7 @@
         <v>264</v>
       </c>
       <c r="D56" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2735,7 +2741,7 @@
         <v>264</v>
       </c>
       <c r="D57" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2749,7 +2755,7 @@
         <v>264</v>
       </c>
       <c r="D58" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2763,7 +2769,7 @@
         <v>266</v>
       </c>
       <c r="D59" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2777,7 +2783,7 @@
         <v>264</v>
       </c>
       <c r="D60" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2791,7 +2797,7 @@
         <v>264</v>
       </c>
       <c r="D61" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2805,7 +2811,7 @@
         <v>264</v>
       </c>
       <c r="D62" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2819,7 +2825,7 @@
         <v>268</v>
       </c>
       <c r="D63" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2833,7 +2839,7 @@
         <v>266</v>
       </c>
       <c r="D64" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2847,7 +2853,7 @@
         <v>266</v>
       </c>
       <c r="D65" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2861,7 +2867,7 @@
         <v>268</v>
       </c>
       <c r="D66" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2875,7 +2881,7 @@
         <v>266</v>
       </c>
       <c r="D67" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2889,7 +2895,7 @@
         <v>267</v>
       </c>
       <c r="D68" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2903,7 +2909,7 @@
         <v>267</v>
       </c>
       <c r="D69" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2917,7 +2923,7 @@
         <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2931,7 +2937,7 @@
         <v>266</v>
       </c>
       <c r="D71" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2945,7 +2951,7 @@
         <v>266</v>
       </c>
       <c r="D72" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2959,7 +2965,7 @@
         <v>268</v>
       </c>
       <c r="D73" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2973,7 +2979,7 @@
         <v>268</v>
       </c>
       <c r="D74" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2987,7 +2993,7 @@
         <v>267</v>
       </c>
       <c r="D75" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3001,7 +3007,7 @@
         <v>268</v>
       </c>
       <c r="D76" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3015,7 +3021,7 @@
         <v>265</v>
       </c>
       <c r="D77" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3029,7 +3035,7 @@
         <v>265</v>
       </c>
       <c r="D78" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3043,7 +3049,7 @@
         <v>265</v>
       </c>
       <c r="D79" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3057,7 +3063,7 @@
         <v>265</v>
       </c>
       <c r="D80" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3071,7 +3077,7 @@
         <v>265</v>
       </c>
       <c r="D81" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3085,7 +3091,7 @@
         <v>265</v>
       </c>
       <c r="D82" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3099,7 +3105,7 @@
         <v>268</v>
       </c>
       <c r="D83" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3113,7 +3119,7 @@
         <v>266</v>
       </c>
       <c r="D84" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3127,7 +3133,7 @@
         <v>268</v>
       </c>
       <c r="D85" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3141,7 +3147,7 @@
         <v>268</v>
       </c>
       <c r="D86" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3155,7 +3161,7 @@
         <v>268</v>
       </c>
       <c r="D87" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3169,7 +3175,7 @@
         <v>268</v>
       </c>
       <c r="D88" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3183,7 +3189,7 @@
         <v>264</v>
       </c>
       <c r="D89" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3197,7 +3203,7 @@
         <v>264</v>
       </c>
       <c r="D90" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3211,7 +3217,7 @@
         <v>264</v>
       </c>
       <c r="D91" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3225,7 +3231,7 @@
         <v>264</v>
       </c>
       <c r="D92" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3239,7 +3245,7 @@
         <v>264</v>
       </c>
       <c r="D93" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3253,7 +3259,7 @@
         <v>264</v>
       </c>
       <c r="D94" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3267,7 +3273,7 @@
         <v>264</v>
       </c>
       <c r="D95" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3281,7 +3287,7 @@
         <v>264</v>
       </c>
       <c r="D96" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3295,7 +3301,7 @@
         <v>264</v>
       </c>
       <c r="D97" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3309,7 +3315,7 @@
         <v>264</v>
       </c>
       <c r="D98" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3323,7 +3329,7 @@
         <v>264</v>
       </c>
       <c r="D99" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3337,7 +3343,7 @@
         <v>264</v>
       </c>
       <c r="D100" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3351,7 +3357,7 @@
         <v>264</v>
       </c>
       <c r="D101" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3365,7 +3371,7 @@
         <v>264</v>
       </c>
       <c r="D102" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3379,7 +3385,7 @@
         <v>264</v>
       </c>
       <c r="D103" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3393,7 +3399,7 @@
         <v>264</v>
       </c>
       <c r="D104" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3407,7 +3413,7 @@
         <v>266</v>
       </c>
       <c r="D105" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3421,7 +3427,7 @@
         <v>266</v>
       </c>
       <c r="D106" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3435,7 +3441,7 @@
         <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3449,7 +3455,7 @@
         <v>266</v>
       </c>
       <c r="D108" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3463,7 +3469,7 @@
         <v>267</v>
       </c>
       <c r="D109" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3477,7 +3483,7 @@
         <v>267</v>
       </c>
       <c r="D110" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3488,10 +3494,10 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D111" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3505,7 +3511,7 @@
         <v>267</v>
       </c>
       <c r="D112" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3519,7 +3525,7 @@
         <v>267</v>
       </c>
       <c r="D113" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3533,7 +3539,7 @@
         <v>267</v>
       </c>
       <c r="D114" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3547,7 +3553,7 @@
         <v>264</v>
       </c>
       <c r="D115" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3561,7 +3567,7 @@
         <v>266</v>
       </c>
       <c r="D116" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3575,7 +3581,7 @@
         <v>266</v>
       </c>
       <c r="D117" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3589,7 +3595,7 @@
         <v>266</v>
       </c>
       <c r="D118" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3603,7 +3609,7 @@
         <v>266</v>
       </c>
       <c r="D119" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3617,7 +3623,7 @@
         <v>266</v>
       </c>
       <c r="D120" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3631,7 +3637,7 @@
         <v>267</v>
       </c>
       <c r="D121" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3645,7 +3651,7 @@
         <v>267</v>
       </c>
       <c r="D122" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3659,7 +3665,7 @@
         <v>267</v>
       </c>
       <c r="D123" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3673,7 +3679,7 @@
         <v>267</v>
       </c>
       <c r="D124" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3687,7 +3693,7 @@
         <v>267</v>
       </c>
       <c r="D125" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3701,7 +3707,7 @@
         <v>264</v>
       </c>
       <c r="D126" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3715,7 +3721,7 @@
         <v>267</v>
       </c>
       <c r="D127" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3729,7 +3735,7 @@
         <v>264</v>
       </c>
       <c r="D128" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3743,7 +3749,7 @@
         <v>264</v>
       </c>
       <c r="D129" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3757,7 +3763,7 @@
         <v>264</v>
       </c>
       <c r="D130" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3771,7 +3777,7 @@
         <v>264</v>
       </c>
       <c r="D131" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3785,7 +3791,7 @@
         <v>264</v>
       </c>
       <c r="D132" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3799,7 +3805,7 @@
         <v>264</v>
       </c>
       <c r="D133" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3813,7 +3819,7 @@
         <v>264</v>
       </c>
       <c r="D134" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3827,7 +3833,7 @@
         <v>264</v>
       </c>
       <c r="D135" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3841,7 +3847,7 @@
         <v>268</v>
       </c>
       <c r="D136" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3855,7 +3861,7 @@
         <v>266</v>
       </c>
       <c r="D137" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3869,7 +3875,7 @@
         <v>266</v>
       </c>
       <c r="D138" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3883,7 +3889,7 @@
         <v>266</v>
       </c>
       <c r="D139" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3897,7 +3903,7 @@
         <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3908,10 +3914,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="D141" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3925,7 +3931,7 @@
         <v>266</v>
       </c>
       <c r="D142" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3939,7 +3945,7 @@
         <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3953,7 +3959,7 @@
         <v>265</v>
       </c>
       <c r="D144" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3967,7 +3973,7 @@
         <v>265</v>
       </c>
       <c r="D145" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3981,7 +3987,7 @@
         <v>265</v>
       </c>
       <c r="D146" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3995,7 +4001,7 @@
         <v>265</v>
       </c>
       <c r="D147" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4009,7 +4015,7 @@
         <v>268</v>
       </c>
       <c r="D148" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4023,7 +4029,7 @@
         <v>264</v>
       </c>
       <c r="D149" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4037,7 +4043,7 @@
         <v>267</v>
       </c>
       <c r="D150" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4051,7 +4057,7 @@
         <v>264</v>
       </c>
       <c r="D151" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4065,7 +4071,7 @@
         <v>267</v>
       </c>
       <c r="D152" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4079,7 +4085,7 @@
         <v>264</v>
       </c>
       <c r="D153" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4093,7 +4099,7 @@
         <v>266</v>
       </c>
       <c r="D154" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4107,7 +4113,7 @@
         <v>264</v>
       </c>
       <c r="D155" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4121,7 +4127,7 @@
         <v>266</v>
       </c>
       <c r="D156" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4135,7 +4141,7 @@
         <v>264</v>
       </c>
       <c r="D157" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4149,7 +4155,7 @@
         <v>264</v>
       </c>
       <c r="D158" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4163,7 +4169,7 @@
         <v>264</v>
       </c>
       <c r="D159" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4177,7 +4183,7 @@
         <v>264</v>
       </c>
       <c r="D160" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4191,7 +4197,7 @@
         <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4205,7 +4211,7 @@
         <v>267</v>
       </c>
       <c r="D162" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4219,7 +4225,7 @@
         <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4233,7 +4239,7 @@
         <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4247,7 +4253,7 @@
         <v>264</v>
       </c>
       <c r="D165" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4261,7 +4267,7 @@
         <v>264</v>
       </c>
       <c r="D166" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4275,7 +4281,7 @@
         <v>264</v>
       </c>
       <c r="D167" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4289,7 +4295,7 @@
         <v>264</v>
       </c>
       <c r="D168" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4303,7 +4309,7 @@
         <v>264</v>
       </c>
       <c r="D169" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4317,7 +4323,7 @@
         <v>264</v>
       </c>
       <c r="D170" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4331,7 +4337,7 @@
         <v>264</v>
       </c>
       <c r="D171" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4345,7 +4351,7 @@
         <v>264</v>
       </c>
       <c r="D172" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4359,7 +4365,7 @@
         <v>264</v>
       </c>
       <c r="D173" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4373,7 +4379,7 @@
         <v>267</v>
       </c>
       <c r="D174" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4387,7 +4393,7 @@
         <v>264</v>
       </c>
       <c r="D175" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4401,7 +4407,7 @@
         <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4415,7 +4421,7 @@
         <v>264</v>
       </c>
       <c r="D177" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4429,7 +4435,7 @@
         <v>264</v>
       </c>
       <c r="D178" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4443,7 +4449,7 @@
         <v>264</v>
       </c>
       <c r="D179" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4457,7 +4463,7 @@
         <v>264</v>
       </c>
       <c r="D180" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4471,7 +4477,7 @@
         <v>266</v>
       </c>
       <c r="D181" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4485,7 +4491,7 @@
         <v>264</v>
       </c>
       <c r="D182" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4499,7 +4505,7 @@
         <v>266</v>
       </c>
       <c r="D183" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4513,7 +4519,7 @@
         <v>266</v>
       </c>
       <c r="D184" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4527,7 +4533,7 @@
         <v>266</v>
       </c>
       <c r="D185" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4541,7 +4547,7 @@
         <v>268</v>
       </c>
       <c r="D186" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4555,7 +4561,7 @@
         <v>266</v>
       </c>
       <c r="D187" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4569,7 +4575,7 @@
         <v>266</v>
       </c>
       <c r="D188" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4583,7 +4589,7 @@
         <v>266</v>
       </c>
       <c r="D189" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4597,7 +4603,7 @@
         <v>266</v>
       </c>
       <c r="D190" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4611,7 +4617,7 @@
         <v>266</v>
       </c>
       <c r="D191" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4625,7 +4631,7 @@
         <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4639,7 +4645,7 @@
         <v>266</v>
       </c>
       <c r="D193" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4653,7 +4659,7 @@
         <v>266</v>
       </c>
       <c r="D194" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4667,7 +4673,7 @@
         <v>266</v>
       </c>
       <c r="D195" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4681,7 +4687,7 @@
         <v>266</v>
       </c>
       <c r="D196" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4695,7 +4701,7 @@
         <v>266</v>
       </c>
       <c r="D197" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4709,7 +4715,7 @@
         <v>267</v>
       </c>
       <c r="D198" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4723,7 +4729,7 @@
         <v>267</v>
       </c>
       <c r="D199" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4737,7 +4743,7 @@
         <v>267</v>
       </c>
       <c r="D200" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4751,7 +4757,7 @@
         <v>264</v>
       </c>
       <c r="D201" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4765,7 +4771,7 @@
         <v>267</v>
       </c>
       <c r="D202" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4779,7 +4785,7 @@
         <v>267</v>
       </c>
       <c r="D203" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4793,7 +4799,7 @@
         <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4807,7 +4813,7 @@
         <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4821,7 +4827,7 @@
         <v>266</v>
       </c>
       <c r="D206" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4835,7 +4841,7 @@
         <v>264</v>
       </c>
       <c r="D207" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4849,7 +4855,7 @@
         <v>266</v>
       </c>
       <c r="D208" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4863,7 +4869,7 @@
         <v>266</v>
       </c>
       <c r="D209" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4877,7 +4883,7 @@
         <v>266</v>
       </c>
       <c r="D210" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4891,7 +4897,7 @@
         <v>266</v>
       </c>
       <c r="D211" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4905,7 +4911,7 @@
         <v>266</v>
       </c>
       <c r="D212" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4919,7 +4925,7 @@
         <v>264</v>
       </c>
       <c r="D213" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4933,7 +4939,7 @@
         <v>264</v>
       </c>
       <c r="D214" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4947,7 +4953,7 @@
         <v>264</v>
       </c>
       <c r="D215" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4961,7 +4967,7 @@
         <v>264</v>
       </c>
       <c r="D216" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4975,7 +4981,7 @@
         <v>264</v>
       </c>
       <c r="D217" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4989,7 +4995,7 @@
         <v>264</v>
       </c>
       <c r="D218" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5003,7 +5009,7 @@
         <v>264</v>
       </c>
       <c r="D219" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5017,7 +5023,7 @@
         <v>264</v>
       </c>
       <c r="D220" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5031,7 +5037,7 @@
         <v>266</v>
       </c>
       <c r="D221" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5045,7 +5051,7 @@
         <v>266</v>
       </c>
       <c r="D222" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5056,10 +5062,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="D223" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5073,7 +5079,7 @@
         <v>266</v>
       </c>
       <c r="D224" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5087,7 +5093,7 @@
         <v>266</v>
       </c>
       <c r="D225" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5101,7 +5107,7 @@
         <v>266</v>
       </c>
       <c r="D226" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5115,7 +5121,7 @@
         <v>266</v>
       </c>
       <c r="D227" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5129,7 +5135,7 @@
         <v>266</v>
       </c>
       <c r="D228" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5143,7 +5149,7 @@
         <v>266</v>
       </c>
       <c r="D229" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5157,7 +5163,7 @@
         <v>266</v>
       </c>
       <c r="D230" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5171,7 +5177,7 @@
         <v>266</v>
       </c>
       <c r="D231" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5185,7 +5191,7 @@
         <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5199,7 +5205,7 @@
         <v>266</v>
       </c>
       <c r="D233" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5213,7 +5219,7 @@
         <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5227,7 +5233,7 @@
         <v>264</v>
       </c>
       <c r="D235" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5241,7 +5247,7 @@
         <v>264</v>
       </c>
       <c r="D236" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5255,7 +5261,7 @@
         <v>264</v>
       </c>
       <c r="D237" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5269,7 +5275,7 @@
         <v>264</v>
       </c>
       <c r="D238" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5283,7 +5289,7 @@
         <v>264</v>
       </c>
       <c r="D239" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5297,7 +5303,7 @@
         <v>264</v>
       </c>
       <c r="D240" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5311,7 +5317,7 @@
         <v>264</v>
       </c>
       <c r="D241" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5325,7 +5331,7 @@
         <v>264</v>
       </c>
       <c r="D242" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5339,7 +5345,7 @@
         <v>266</v>
       </c>
       <c r="D243" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5353,7 +5359,7 @@
         <v>266</v>
       </c>
       <c r="D244" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5367,7 +5373,7 @@
         <v>266</v>
       </c>
       <c r="D245" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5381,7 +5387,7 @@
         <v>266</v>
       </c>
       <c r="D246" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5395,7 +5401,7 @@
         <v>266</v>
       </c>
       <c r="D247" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5409,7 +5415,7 @@
         <v>265</v>
       </c>
       <c r="D248" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5423,7 +5429,7 @@
         <v>266</v>
       </c>
       <c r="D249" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5437,7 +5443,7 @@
         <v>266</v>
       </c>
       <c r="D250" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5451,7 +5457,7 @@
         <v>264</v>
       </c>
       <c r="D251" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5465,7 +5471,7 @@
         <v>265</v>
       </c>
       <c r="D252" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5479,7 +5485,7 @@
         <v>265</v>
       </c>
       <c r="D253" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5493,7 +5499,7 @@
         <v>265</v>
       </c>
       <c r="D254" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5507,7 +5513,7 @@
         <v>265</v>
       </c>
       <c r="D255" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5521,7 +5527,7 @@
         <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
